--- a/static/brand/HML-QT-Quotation-Letterhead.xlsx
+++ b/static/brand/HML-QT-Quotation-Letterhead.xlsx
@@ -62,7 +62,7 @@
     <t>2nd Floor, 68 Nguyen Hue, Sai Gon Ward, HCMC, Vietnam</t>
   </si>
   <si>
-    <t>www.humiley.com   ·   contact@humiley.com   ·   +84 90 9840 714</t>
+    <t>www.humiley.com   ·   contact@humiley.com   ·   +84 2877776668</t>
   </si>
   <si>
     <t>Ho Chi Minh City, {DATE}</t>
